--- a/Dataset/rooms_dataset.xlsx
+++ b/Dataset/rooms_dataset.xlsx
@@ -422,15 +422,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
@@ -533,7 +533,11 @@
           <t>room1_img4.jpg</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>room1_img5.jpg</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Kripal Nagar, Bhilai, Chhattisgarh</t>
@@ -581,18 +585,30 @@
           <t>room2_img1.jpg</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>room2_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>room2_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>room2_img4.jpg</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>M Pocket, Bhilai, Chhattisgarh</t>
+          <t>Jawahar nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -607,17 +623,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CCTV, Parking, Water Supply, Wifi</t>
+          <t>Kitchen, Parking</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -654,17 +670,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Baikunth Nagar, Bhilai, Chhattisgarh</t>
+          <t>Sector 5, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>700</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>furnished</t>
+          <t>Unfurnished</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +690,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Parking, Table</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -684,7 +700,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -709,21 +725,29 @@
           <t>room4_img3.jpg</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>room4_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>room4_img5.jpg</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Housing Board Colony, Bhilai, Chhattisgarh</t>
+          <t>Jamul, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>350</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Semi-furnished</t>
+          <t>Unfurnished</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -733,12 +757,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Kitchen, Parking</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -768,16 +792,24 @@
           <t>room5_img3.jpg</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>room5_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>room5_img5.jpg</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jawahar nagar, Bhilai, Chhattisgarh</t>
+          <t>Supela, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -792,12 +824,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kitchen, Parking</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -817,39 +849,23 @@
           <t>room6_img1.jpg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>room6_img2.jpg</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>room6_img3.jpg</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>room6_img4.jpg</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>room6_img5.jpg</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sector 5, Bhilai, Chhattisgarh</t>
+          <t>Housing Board Colony, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>350</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Unfurnished</t>
+          <t>Semi-furnished</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -859,12 +875,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Parking, Table</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -894,36 +910,44 @@
           <t>room7_img3.jpg</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>room7_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>room7_img5.jpg</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Housing Board Colony, Bhilai, Chhattisgarh</t>
+          <t>Ram nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Semi-furnished</t>
+          <t>Unfurnished</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Kitchen, Parking</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -953,19 +977,11 @@
           <t>room8_img3.jpg</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>room8_img4.jpg</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>room8_img5.jpg</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rajiv Nagar, Bhilai, Chhattisgarh</t>
+          <t>Ram nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -975,7 +991,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Unfurnished</t>
+          <t>Semi-furnished</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -985,12 +1001,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Kitchen, Parking</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1015,17 +1031,29 @@
           <t>room9_img2.jpg</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>room9_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>room9_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>room9_img5.jpg</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Khursipar, Bhilai, Chhattisgarh</t>
+          <t>Supela, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>350</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1040,17 +1068,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Attached Bathroom, Kitchen, Parking, Water Supply</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1075,21 +1103,29 @@
           <t>room10_img3.jpg</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>room10_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>room10_img5.jpg</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jawahar nagar, Bhilai, Chhattisgarh</t>
+          <t>Vaishali Nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Unfurnished</t>
+          <t>furnished</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1099,12 +1135,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Parking, Water Supply</t>
+          <t>Kitchen, Parking</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1146,17 +1182,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Supela, Bhilai, Chhattisgarh</t>
+          <t>Kripal Nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Semi-furnished</t>
+          <t>Unfurnished</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1171,12 +1207,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1201,20 +1237,16 @@
           <t>room12_img3.jpg</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>room12_img4.jpg</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Baikunth Nagar, Bhilai, Chhattisgarh</t>
+          <t>Supele Market, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1234,7 +1266,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1254,30 +1286,18 @@
           <t>room13_img1.jpg</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>room13_img2.jpg</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>room13_img3.jpg</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>room13_img4.jpg</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kripal Nagar, Bhilai, Chhattisgarh</t>
+          <t>Jawahar nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1292,17 +1312,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Parking, Table</t>
+          <t>Bed, Parking, Table, Water Supply</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1322,34 +1342,22 @@
           <t>room14_img2.jpg</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>room14_img3.jpg</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>room14_img4.jpg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>room14_img5.jpg</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ram nagar, Bhilai, Chhattisgarh</t>
+          <t>Maroda Tank, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Unfurnished</t>
+          <t>furnished</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1359,17 +1367,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Kitchen, Parking</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1394,16 +1402,20 @@
           <t>room15_img3.jpg</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>room15_img4.jpg</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ram nagar, Bhilai, Chhattisgarh</t>
+          <t>Maitri Kunj, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1418,12 +1430,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Kitchen, Parking</t>
+          <t>Parking, Water Supply</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1453,36 +1465,44 @@
           <t>room16_img3.jpg</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>room16_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>room16_img5.jpg</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Supela, Bhilai, Chhattisgarh</t>
+          <t>Risali, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Unfurnished</t>
+          <t>Semi-furnished</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Attached Bathroom, Kitchen, Parking, Water Supply</t>
+          <t>Bed, Parking, Table, Water Supply</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1502,30 +1522,18 @@
           <t>room17_img1.jpg</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>room17_img2.jpg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>room17_img3.jpg</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>room17_img4.jpg</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vaishali Nagar, Bhilai, Chhattisgarh</t>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1540,17 +1548,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Kitchen, Parking</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1565,39 +1573,23 @@
           <t>room18_img1.jpg</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>room18_img2.jpg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>room18_img3.jpg</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>room18_img4.jpg</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>room18_img5.jpg</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kripal Nagar, Bhilai, Chhattisgarh</t>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>85459</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Unfurnished</t>
+          <t>furnished</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1605,19 +1597,15 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Parking</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1632,39 +1620,23 @@
           <t>room19_img1.jpg</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>room19_img2.jpg</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>room19_img3.jpg</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>room19_img4.jpg</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>room19_img5.jpg</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Vaishali Nagar, Bhilai, Chhattisgarh</t>
+          <t>Katulbod, Durg, Chhattisgarh</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Unfurnished</t>
+          <t>Semi-furnished</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,17 +1646,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Parking, Water Supply</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1704,22 +1676,26 @@
           <t>room20_img2.jpg</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>room20_img3.jpg</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Supele Market, Bhilai, Chhattisgarh</t>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Semi-furnished</t>
+          <t>Unfurnished</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1734,7 +1710,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1760,35 +1736,5889 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jawahar nagar, Bhilai, Chhattisgarh</t>
+          <t>Radhika Nagar, Bhilai, Chhattisgarh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>room22_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>room22_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>room22_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>room22_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Padmanabhpur, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Bed, Parking</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>room23_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>room23_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>room23_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>room23_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>room23_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Daya Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Bed, Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>room24_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>room24_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>room24_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>room25_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>room25_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>room25_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>room25_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>room25_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>room26_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>room26_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>room26_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>room26_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>room26_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>room27_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>room27_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>room27_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>room27_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>room27_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Kitchen, Parking, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>room28_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>room28_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>room28_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>room28_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>room28_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Surya Residence Apartment, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>room29_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>room29_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hari Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>room30_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>room30_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>room30_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>room30_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>room30_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>room31_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>room31_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>room31_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>room31_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>room31_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>room32_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>room32_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Kohka Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>room33_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>room33_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>room33_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>room33_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>room33_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ruabandha, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>room34_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>room34_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>room34_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>room34_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>room34_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Adarsh Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>room35_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>room35_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>room35_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>room35_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>room35_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Muktanagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>furnished</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Bed, Parking, Table, Water Supply</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>room36_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>room36_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>room36_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>room36_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>room37_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>room37_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>room37_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>room37_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>room37_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Vishwa Bank Housing Board Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Parking, Table</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>room38_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>room38_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>room38_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>room38_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>room38_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Minakshi Nagar, Durg-Bhilainagar, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>room39_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>room39_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>room39_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>room39_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>room39_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Daya Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Bed, Kitchen, Parking, Table</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>room40_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>room40_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Surya Vihar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>room41_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking, Table</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>room42_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>room42_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>room42_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>room42_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>room42_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Kurud, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>room43_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>room43_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>room43_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Bed, Fridge, Kitchen, Parking, Wifi</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>room44_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>room45_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>room45_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>room46_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>room46_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>room46_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>room46_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ispat Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>room47_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>room48_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>room48_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>room49_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Chauhan Town, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Parking</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>room50_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>room50_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>room50_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>room50_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>room50_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>room51_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ganesh Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>room52_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>room52_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>room52_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bed, CCTV, Kitchen, Parking, Security, Table, Water Supply, Wifi</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>room53_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>room53_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>room53_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>room54_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>room55_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>room55_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>room56_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Kohka Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Bed, Parking</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>room57_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>room57_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>room57_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>room57_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>room57_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Borsi Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>room58_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hudco, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Bed, Parking, Sofa, Table</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>room59_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>room59_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Kurud, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>room60_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chauhan Town, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>room61_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chauhan Town, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>room62_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>room62_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>room62_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>room62_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>room62_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hudco, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>14000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>room63_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>room63_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>room63_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>room63_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>room64_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>room64_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>room64_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>room64_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>room64_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hanuman Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bed, Fridge, Parking, Sofa, Table, Washing Machine, Water Supply</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>room65_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Parking</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>room66_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>room66_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>room66_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>room66_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>room66_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Parking, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>room67_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>room67_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>room68_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Bed, Parking, Table</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>room69_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Mahadev Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>room70_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sharing room for girl near dominoz new adarsh nagar durg</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>room71_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>room72_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Shivaji Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>room73_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>room73_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Parking, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>room74_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>room74_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>room75_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>room75_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>room75_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>room76_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>room76_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>room76_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>room76_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking, Water Supply</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>room77_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>room77_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>room77_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>room77_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Chauhan Town, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>room78_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Arya Nagar Near Buddha Vihar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>room79_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>room79_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Mahesh Colony, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>room80_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>room80_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>room80_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>room80_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Om nagar urla durg</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Parking, Water Supply</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>room81_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>room81_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>room81_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>room81_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>room81_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Harna Bandha, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>room82_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hasharidih Durg, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>room83_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>room83_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>room83_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>room83_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>room83_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>room84_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>room84_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>room84_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>room84_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Risali Village, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>room85_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>room85_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>room85_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>room85_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>room85_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Kohka Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bed, Fan, Fridge, Kitchen, Parking, Table</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>room86_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>room86_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>room86_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>room86_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>room86_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Bed, Fridge, Parking, Security</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>room87_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>room87_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>room87_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>room87_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>room87_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking, Security, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>room88_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Laxmi Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>room89_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Risali, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>room90_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>room90_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>room90_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>room90_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>room90_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Maitri Kunj, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>room91_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>room91_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>room91_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>room91_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>room91_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Pragati Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bed, Parking, Table, Water Supply, Wifi</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>room92_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>room92_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>room92_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Pushpak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Bed, Parking, Table</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>room93_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>room93_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>room93_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>room93_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>room93_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>CCTV, Kitchen, Parking, Security, Table, Water Supply, Wifi</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>6999</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>room94_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>room94_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>room94_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>room94_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>room94_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Anand Vihar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>room95_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>room95_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Kitchen, Parking, Water Supply, Wifi</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>room96_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>room96_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>room96_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>room96_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>room96_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bed, Parking, Security, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>room97_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>room97_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>room97_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Parking, Water Supply</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>room98_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>room98_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>room98_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>room98_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>room98_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bed, Parking, Table</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>room99_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>room99_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>room99_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>room99_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>room99_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Parking, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>room100_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>room100_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>room100_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>room100_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>room100_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking, Security, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>room101_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Kurud, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>room102_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>room102_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ispat Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>room103_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>room103_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>room103_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>room103_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>room103_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Patan, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Fridge, Kitchen, Parking, Security, Table, Wifi</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t>2600</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>room104_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>room104_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Risali, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>AC, Attached Bathroom, Fridge, Table</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>room105_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>room105_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>room105_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>room105_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>room105_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Kohka Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Fridge, Parking, Washing Machine, Water Supply, Wifi</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>room106_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>room106_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>room106_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>AC, Fridge, Parking, Security, Water Supply</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>room107_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Patan, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>room108_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>room108_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>room108_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>room108_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Pragati Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Bed, Table, Water Supply</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>room109_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>room109_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>room109_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>room109_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>room109_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Baghera, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Parking, Water Supply</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>room110_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>room110_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>room110_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>room110_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Shikshak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>room111_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>room111_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>room111_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>room111_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>room111_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>address - Gupta girls PG , infront of old water tank , budhha vihar ke backside , arya nagar durg (c.g.)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Parking, Water Supply</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>room112_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>room112_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Sector 6, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>room113_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>room113_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>room113_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>room113_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>room113_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ayyapa Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Parking, Table, Washing Machine</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>room114_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>room114_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>room114_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>room114_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>room114_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>AC, Parking, Water Supply, Wifi</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>room115_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>room115_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>room115_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Maitri Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Attached Bathroom, Parking</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>room116_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>room116_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>room116_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Unfurnished</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Parking, Water Supply</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>room117_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>State Bank Colony Near Sector 7, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bed, Parking</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>room118_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>room118_img2.jpg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>room118_img3.jpg</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>room118_img4.jpg</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>room118_img5.jpg</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>room119_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Agarsen Chowk, Durg-Bhilainagar, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Fridge, Kitchen, Parking</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/Dataset/rooms_dataset.xlsx
+++ b/Dataset/rooms_dataset.xlsx
@@ -422,11 +422,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -7624,6 +7624,5255 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>room_120_img1.webp</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Mannu Chowk, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>1775</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>room_121_img1.webp</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Raj Kishore Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>room_122_img1.webp</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Bandhwapara, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>CCTV</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>room_123_img1.webp</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Shakuntalam, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>room_124_img1.webp</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>room_125_img1.webp</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Tifra Industrial Area, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>room_126_img1.webp</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Balram Talkies Chowk, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>room_127_img1.webp</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Jarhabhata, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>room_128_img1.webp</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Abhishek Vihar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>room_129_img1.webp</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Vinoba Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>room_130_img1.webp</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>room_131_img1.webp</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Vivekanand Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>room_132_img1.webp</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Babji Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>room_133_img1.webp</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Bandhwapara, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>room_134_img1.webp</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Raj Kishore Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>room_135_img1.webp</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Abhilasa Colony, Sirgitti</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>room_136_img1.webp</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Shivam Vihar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>room_137_img1.webp</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Dev Nagar, Koni</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>room_138_img1.webp</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Dayalband, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>room_139_img1.webp</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Lokeshwar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>room_140_img1.webp</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Mangla, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>room_141_img1.webp</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Mannu Chowk, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>room_142_img1.webp</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Raj Kishore Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>room_143_img1.webp</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Attached Bathroom</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>room_144_img1.webp</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Gauri Ganesh Colony, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>room_145_img1.webp</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Mangla, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>room_146_img1.webp</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Hamu Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>room_147_img1.webp</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ganga Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>room_148_img1.webp</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>room_149_img1.webp</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>room_150_img1.webp</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>27 Kholi, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>room_151_img1.webp</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Agyeya Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>room_152_img1.webp</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Juna Bilaspur, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>room_153_img1.webp</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>room_154_img1.webp</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Jarhabhata, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>room_155_img1.webp</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Tiphara, Tifra</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>room_156_img1.webp</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Bengali Para, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>room_157_img1.webp</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>room_158_img1.webp</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Godpara, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>room_159_img1.webp</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Gandhi Chowk, Bilaspur</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>room_160_img1.webp</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Telibandha, Raipur</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>room_161_img1.webp</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Mowa, Raipur</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>room_162_img1.webp</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Nahar Para, Raipur</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>room_163_img1.webp</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Pandri, Raipur</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>room_164_img1.webp</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Rajiv Nagar Colony, Raipur</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>room_165_img1.webp</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Kabeer Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>room_166_img1.webp</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Pachpedi Naka, Raipur</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>room_167_img1.webp</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Kota, Raipur</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>room_168_img1.webp</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Pachpedi Naka, Raipur</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>room_169_img1.webp</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Shyam Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>room_170_img1.webp</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Shyam Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>room_171_img1.webp</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Danganiya, Raipur</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>room_172_img1.webp</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Kotwali Chowk, Raipur</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>room_173_img1.webp</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Matpara, Raipur</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>room_174_img1.webp</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>room_175_img1.webp</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Avanti Vihar Colony, Raipur</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>room_176_img1.webp</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Mowa, Raipur</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>room_177_img1.webp</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Kota, Raipur</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>room_178_img1.webp</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Kanchanjanga Colony, Raipur</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>room_179_img1.webp</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Mowa, Raipur</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>room_180_img1.webp</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Pandri, Raipur</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>room_181_img1.webp</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Pandri, Raipur</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>room_182_img1.webp</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Pachpedi Naka, Raipur</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>room_183_img1.webp</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Mangal Bazar, Raipur</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>room_184_img1.webp</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Kota, Raipur</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>room_185_img1.webp</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Mangal Bazar, Raipur</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>room_186_img1.webp</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Mahavir Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>room_187_img1.webp</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Ravi Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>room_188_img1.webp</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Fafadih, Raipur</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>room_189_img1.webp</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Sunder Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>room_190_img1.webp</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Professor Colony, Raipur</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>room_191_img1.webp</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>New Shanti Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>room_192_img1.webp</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Bhanpuri, Raipur</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>room_193_img1.webp</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Gopiapara, Raipur</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>room_194_img1.webp</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Pandri, Raipur</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>room_195_img1.webp</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>New Rajendra Nagar, Raipur</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>room_196_img1.webp</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Avanti Vihar Colony, Raipur</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>room_197_img1.webp</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Kota Colony, Raipur</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>room_198_img1.webp</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Mominpara, Raipur</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>room_199_img1.webp</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Telibandha, Raipur</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>room_200_img1.webp</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Supele Market, Bhilai</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>room_201_img1.webp</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Kripal Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>room_202_img1.webp</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Jamul, Bhilai</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>room_203_img1.webp</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>room_204_img1.webp</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Ram nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>room_205_img1.webp</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Vaishali Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>room_206_img1.webp</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Kripal Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>room_207_img1.webp</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Housing Board Colony, Bhilai</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>room_208_img1.webp</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Ram nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>room_209_img1.webp</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Vaishali Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>room_210_img1.webp</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Kripal Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>7800</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>room_211_img1.webp</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Supele Market, Bhilai</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>room_212_img1.webp</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Kohka Colony, Bhilai</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>room_213_img1.webp</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Radhika Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>room_214_img1.webp</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Hind Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>room_215_img1.webp</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Arya Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>room_216_img1.webp</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Arya Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>room_217_img1.webp</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>room_218_img1.webp</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Kurud, Bhilai</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>room_219_img1.webp</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Maitri nagar Near Dixit Colony, Bhilai</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>room_220_img1.webp</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>room_221_img1.webp</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Panchsheel Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>room_222_img1.webp</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>room_223_img1.webp</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>room_224_img1.webp</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>room_225_img1.webp</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Awadhpuri Risali, Bhilai</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>room_226_img1.webp</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Pushpak Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>room_227_img1.webp</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Madhuban Nagar, Durg</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>room_228_img1.webp</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>room_229_img1.webp</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Maitri Kunj, Bhilai</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>room_230_img1.webp</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>85459</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dataset/rooms_dataset.xlsx
+++ b/Dataset/rooms_dataset.xlsx
@@ -422,15 +422,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M231"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
@@ -7635,10 +7635,26 @@
           <t>room_120_img1.webp</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>room_120_img2.webp</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>room_120_img3.webp</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>room_120_img4.webp</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>room_120_img5.webp</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>Mannu Chowk, Bilaspur</t>
@@ -7682,10 +7698,26 @@
           <t>room_121_img1.webp</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>room_121_img2.webp</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>room_121_img3.webp</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>room_121_img4.webp</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>room_121_img5.webp</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>Raj Kishore Nagar, Bilaspur</t>
@@ -7780,8 +7812,16 @@
           <t>room_123_img1.webp</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>room_123_img2.webp</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>room_123_img3.webp</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
@@ -7827,10 +7867,26 @@
           <t>room_124_img1.webp</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>room_124_img2.webp</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>room_124_img3.webp</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>room_124_img4.webp</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>room_124_img5.webp</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>Sarkanda, Bilaspur</t>
@@ -7874,8 +7930,16 @@
           <t>room_125_img1.webp</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>room_125_img2.webp</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>room_125_img3.webp</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
@@ -7921,10 +7985,26 @@
           <t>room_126_img1.webp</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>room_126_img2.webp</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>room_126_img3.webp</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>room_126_img4.webp</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>room_126_img5.webp</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>Balram Talkies Chowk, Bilaspur</t>
@@ -7968,8 +8048,16 @@
           <t>room_127_img1.webp</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>room_127_img2.webp</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>room_127_img3.webp</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
@@ -8015,10 +8103,26 @@
           <t>room_128_img1.webp</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>room_128_img2.webp</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>room_128_img3.webp</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>room_128_img4.webp</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>room_128_img5.webp</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>Abhishek Vihar, Bilaspur</t>
@@ -8062,8 +8166,16 @@
           <t>room_129_img1.webp</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>room_129_img2.webp</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>room_129_img3.webp</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
@@ -8109,10 +8221,26 @@
           <t>room_130_img1.webp</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>room_130_img2.webp</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>room_130_img3.webp</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>room_130_img4.webp</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>room_130_img5.webp</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>Sarkanda, Bilaspur</t>
@@ -8156,10 +8284,26 @@
           <t>room_131_img1.webp</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>room_131_img2.webp</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>room_131_img3.webp</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>room_131_img4.webp</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>room_131_img5.webp</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
           <t>Vivekanand Nagar, Bilaspur</t>
@@ -8203,10 +8347,26 @@
           <t>room_132_img1.webp</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>room_132_img2.webp</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>room_132_img3.webp</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>room_132_img4.webp</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>room_132_img5.webp</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t>Babji Nagar, Bilaspur</t>
@@ -8250,10 +8410,26 @@
           <t>room_133_img1.webp</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>room_133_img2.webp</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>room_133_img3.webp</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>room_133_img4.webp</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>room_133_img5.webp</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>Bandhwapara, Bilaspur</t>
@@ -8297,10 +8473,26 @@
           <t>room_134_img1.webp</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>room_134_img2.webp</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>room_134_img3.webp</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>room_134_img4.webp</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>room_134_img5.webp</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>Raj Kishore Nagar, Bilaspur</t>
@@ -8344,8 +8536,16 @@
           <t>room_135_img1.webp</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>room_135_img2.webp</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>room_135_img3.webp</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
@@ -8391,9 +8591,21 @@
           <t>room_136_img1.webp</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>room_136_img2.webp</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>room_136_img3.webp</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>room_136_img4.webp</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
@@ -8442,9 +8654,21 @@
           <t>room_137_img1.webp</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>room_137_img2.webp</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>room_137_img3.webp</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>room_137_img4.webp</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
@@ -8489,10 +8713,26 @@
           <t>room_138_img1.webp</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>room_138_img2.webp</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>room_138_img3.webp</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>room_138_img4.webp</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>room_138_img5.webp</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>Dayalband, Bilaspur</t>
@@ -8536,7 +8776,11 @@
           <t>room_139_img1.webp</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>room_139_img2.webp</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
@@ -8583,10 +8827,26 @@
           <t>room_140_img1.webp</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>room_140_img2.webp</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>room_140_img3.webp</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>room_140_img4.webp</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>room_140_img5.webp</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>Mangla, Bilaspur</t>
@@ -8630,10 +8890,26 @@
           <t>room_141_img1.webp</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>room_141_img2.webp</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>room_141_img3.webp</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>room_141_img4.webp</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>room_141_img5.webp</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>Mannu Chowk, Bilaspur</t>
@@ -8677,10 +8953,26 @@
           <t>room_142_img1.webp</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>room_142_img2.webp</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>room_142_img3.webp</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>room_142_img4.webp</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>room_142_img5.webp</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>Raj Kishore Nagar, Bilaspur</t>
@@ -8724,10 +9016,26 @@
           <t>room_143_img1.webp</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>room_143_img2.webp</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>room_143_img3.webp</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>room_143_img4.webp</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>room_143_img5.webp</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>Sarkanda, Bilaspur</t>
@@ -8869,10 +9177,26 @@
           <t>room_146_img1.webp</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>room_146_img2.webp</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>room_146_img3.webp</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>room_146_img4.webp</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>room_146_img5.webp</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr">
         <is>
           <t>Hamu Nagar, Bilaspur</t>
@@ -8963,7 +9287,11 @@
           <t>room_148_img1.webp</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>room_148_img2.webp</t>
+        </is>
+      </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
@@ -8999,3880 +9327,6 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>room_149_img1.webp</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Sarkanda, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>room_150_img1.webp</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>27 Kholi, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>room_151_img1.webp</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Agyeya Nagar, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>room_152_img1.webp</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Juna Bilaspur, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>room_153_img1.webp</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Sarkanda, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>room_154_img1.webp</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Jarhabhata, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>room_155_img1.webp</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Tiphara, Tifra</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>room_156_img1.webp</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Bengali Para, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>room_157_img1.webp</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Nehru Nagar, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>room_158_img1.webp</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Godpara, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>room_159_img1.webp</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Gandhi Chowk, Bilaspur</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>room_160_img1.webp</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Telibandha, Raipur</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>room_161_img1.webp</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Mowa, Raipur</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>room_162_img1.webp</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Nahar Para, Raipur</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>room_163_img1.webp</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Pandri, Raipur</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>room_164_img1.webp</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Rajiv Nagar Colony, Raipur</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>room_165_img1.webp</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Kabeer Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>room_166_img1.webp</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Pachpedi Naka, Raipur</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>furnished</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>4300</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>room_167_img1.webp</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Kota, Raipur</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>room_168_img1.webp</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Pachpedi Naka, Raipur</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>room_169_img1.webp</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Shyam Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>room_170_img1.webp</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Shyam Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>furnished</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>150000</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>room_171_img1.webp</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Danganiya, Raipur</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>room_172_img1.webp</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Kotwali Chowk, Raipur</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>room_173_img1.webp</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Matpara, Raipur</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>room_174_img1.webp</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Deendayal Upadhyaya Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>room_175_img1.webp</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Avanti Vihar Colony, Raipur</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>room_176_img1.webp</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Mowa, Raipur</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>room_177_img1.webp</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Kota, Raipur</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>4700</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>room_178_img1.webp</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Kanchanjanga Colony, Raipur</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>room_179_img1.webp</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Mowa, Raipur</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>room_180_img1.webp</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Pandri, Raipur</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>room_181_img1.webp</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Pandri, Raipur</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>room_182_img1.webp</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Pachpedi Naka, Raipur</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>room_183_img1.webp</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Mangal Bazar, Raipur</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>room_184_img1.webp</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Kota, Raipur</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>room_185_img1.webp</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Mangal Bazar, Raipur</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>room_186_img1.webp</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Mahavir Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>13000</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>room_187_img1.webp</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Ravi Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>room_188_img1.webp</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Fafadih, Raipur</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>furnished</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>room_189_img1.webp</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Sunder Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>room_190_img1.webp</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Professor Colony, Raipur</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>3750</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>room_191_img1.webp</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>New Shanti Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>room_192_img1.webp</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Bhanpuri, Raipur</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>3800</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>room_193_img1.webp</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Gopiapara, Raipur</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>room_194_img1.webp</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Pandri, Raipur</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>room_195_img1.webp</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>New Rajendra Nagar, Raipur</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>room_196_img1.webp</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Avanti Vihar Colony, Raipur</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>furnished</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>room_197_img1.webp</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Kota Colony, Raipur</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>7500</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>room_198_img1.webp</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Mominpara, Raipur</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>room_199_img1.webp</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Telibandha, Raipur</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>room_200_img1.webp</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Supele Market, Bhilai</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>room_201_img1.webp</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Kripal Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>room_202_img1.webp</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Jamul, Bhilai</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>room_203_img1.webp</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Shanti Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>room_204_img1.webp</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Ram nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>room_205_img1.webp</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Vaishali Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>1760</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>room_206_img1.webp</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Kripal Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>room_207_img1.webp</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Housing Board Colony, Bhilai</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>room_208_img1.webp</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Ram nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>room_209_img1.webp</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Vaishali Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>furnished</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>room_210_img1.webp</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Kripal Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>7800</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>room_211_img1.webp</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Supele Market, Bhilai</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>room_212_img1.webp</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Kohka Colony, Bhilai</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>room_213_img1.webp</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Radhika Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>3800</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>room_214_img1.webp</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Hind Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>room_215_img1.webp</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Arya Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>room_216_img1.webp</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Arya Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>room_217_img1.webp</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Nehru Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>room_218_img1.webp</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Kurud, Bhilai</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>room_219_img1.webp</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Maitri nagar Near Dixit Colony, Bhilai</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>room_220_img1.webp</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Shanti Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>room_221_img1.webp</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Panchsheel Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>room_222_img1.webp</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Junwani, Bhilai</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>room_223_img1.webp</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Smriti Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>room_224_img1.webp</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Smriti Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>room_225_img1.webp</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Awadhpuri Risali, Bhilai</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>room_226_img1.webp</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Pushpak Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>room_227_img1.webp</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Madhuban Nagar, Durg</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>room_228_img1.webp</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Nehru Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>room_229_img1.webp</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Maitri Kunj, Bhilai</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>8500</t>
-        </is>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>room_230_img1.webp</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Smriti Nagar, Bhilai</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>85459</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dataset/rooms_dataset.xlsx
+++ b/Dataset/rooms_dataset.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>85459</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1597,7 +1597,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>3500</t>
@@ -1943,7 +1947,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>5000</t>
@@ -2194,7 +2202,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2329,7 +2337,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2379,7 +2391,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2392,7 +2404,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>3750</t>
@@ -2828,7 +2844,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2920,7 +2936,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3017,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3453,7 +3469,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3571,7 +3587,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3596,7 +3612,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3769,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>6000</t>
@@ -3842,7 +3862,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4091,7 +4111,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4162,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4558,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4589,7 +4609,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4635,12 +4655,12 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sharing room for girl near dominoz new adarsh nagar durg</t>
+          <t>Sharing room for girl near dominoz new adarsh nagar durg, Chhattisgarh</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5143,7 +5163,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5156,7 +5176,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>4000</t>
@@ -5197,7 +5221,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Om nagar urla durg</t>
+          <t>Om nagar urla durg, Chhattisgarh</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5387,7 +5411,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5412,7 +5436,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5474,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5475,7 +5499,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5541,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5542,7 +5566,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5608,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5609,7 +5633,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5675,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5676,7 +5700,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5726,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5727,7 +5751,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5777,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5766,7 +5790,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>8500</t>
@@ -5816,7 +5844,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5841,7 +5869,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5911,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5908,7 +5936,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5970,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5967,7 +5995,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6037,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6034,7 +6062,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6104,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6101,7 +6129,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6159,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6156,7 +6184,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6226,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6223,7 +6251,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6285,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6282,7 +6310,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6352,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6349,7 +6377,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6419,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6416,7 +6444,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6486,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6483,7 +6511,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6537,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6534,7 +6562,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6592,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6589,7 +6617,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6659,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6656,7 +6684,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6714,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6711,7 +6739,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6781,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6778,7 +6806,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6840,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6837,7 +6865,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6891,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6888,7 +6916,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6954,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6993,7 +7021,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7018,7 +7046,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7084,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7069,7 +7097,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>3000</t>
@@ -7077,7 +7109,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7114,12 +7146,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>address - Gupta girls PG , infront of old water tank , budhha vihar ke backside , arya nagar durg (c.g.)</t>
+          <t>address - Gupta girls PG , infront of old water tank , budhha vihar ke backside , arya nagar durg (c.g.), Chhattisgarh</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7144,7 +7176,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7206,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7199,7 +7231,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7273,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7266,7 +7298,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7340,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7333,7 +7365,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7399,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7392,7 +7424,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7458,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7451,7 +7483,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7509,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7502,7 +7534,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7576,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7595,7 +7627,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7657,7 +7689,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Mannu Chowk, Bilaspur</t>
+          <t>Mannu Chowk, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7675,7 +7707,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>1775</t>
@@ -7720,7 +7756,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Raj Kishore Nagar, Bilaspur</t>
+          <t>Raj Kishore Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7738,7 +7774,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>4500</t>
@@ -7767,7 +7807,7 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bandhwapara, Bilaspur</t>
+          <t>Bandhwapara, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7826,12 +7866,12 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Shakuntalam, Bilaspur</t>
+          <t>Shakuntalam, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7844,7 +7884,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>2000</t>
@@ -7852,7 +7896,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7933,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarkanda, Bilaspur</t>
+          <t>Sarkanda, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7907,7 +7951,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>1000</t>
@@ -7915,7 +7963,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7992,7 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tifra Industrial Area, Bilaspur</t>
+          <t>Tifra Industrial Area, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7962,7 +8010,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>3500</t>
@@ -8007,7 +8059,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Balram Talkies Chowk, Bilaspur</t>
+          <t>Balram Talkies Chowk, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8025,7 +8077,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>5000</t>
@@ -8062,7 +8118,7 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Jarhabhata, Bilaspur</t>
+          <t>Jarhabhata, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8080,7 +8136,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>4000</t>
@@ -8125,7 +8185,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Abhishek Vihar, Bilaspur</t>
+          <t>Abhishek Vihar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8143,7 +8203,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>4500</t>
@@ -8180,12 +8244,12 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Vinoba Nagar, Bilaspur</t>
+          <t>Vinoba Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8198,7 +8262,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>6000</t>
@@ -8206,7 +8274,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8311,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarkanda, Bilaspur</t>
+          <t>Sarkanda, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8261,7 +8329,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>7000</t>
@@ -8306,7 +8378,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Vivekanand Nagar, Bilaspur</t>
+          <t>Vivekanand Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8324,7 +8396,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>13000</t>
@@ -8369,7 +8445,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Babji Nagar, Bilaspur</t>
+          <t>Babji Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8387,7 +8463,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>3200</t>
@@ -8432,7 +8512,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bandhwapara, Bilaspur</t>
+          <t>Bandhwapara, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8450,7 +8530,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>8000</t>
@@ -8495,7 +8579,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Raj Kishore Nagar, Bilaspur</t>
+          <t>Raj Kishore Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8513,7 +8597,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>4000</t>
@@ -8550,7 +8638,7 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Abhilasa Colony, Sirgitti</t>
+          <t>Abhilasa Colony, Sirgitti, Chhattisgarh</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8568,7 +8656,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>3500</t>
@@ -8609,12 +8701,12 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Shivam Vihar, Bilaspur</t>
+          <t>Shivam Vihar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8672,12 +8764,12 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dev Nagar, Koni</t>
+          <t>Dev Nagar, Koni, Chhattisgarh</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8690,7 +8782,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>2500</t>
@@ -8735,7 +8831,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dayalband, Bilaspur</t>
+          <t>Dayalband, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8753,7 +8849,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>2000</t>
@@ -8786,7 +8886,7 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lokeshwar, Bilaspur</t>
+          <t>Lokeshwar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8804,7 +8904,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>3500</t>
@@ -8849,7 +8953,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Mangla, Bilaspur</t>
+          <t>Mangla, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -8867,7 +8971,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>5200</t>
@@ -8912,7 +9020,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Mannu Chowk, Bilaspur</t>
+          <t>Mannu Chowk, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8930,7 +9038,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>7500</t>
@@ -8975,7 +9087,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Raj Kishore Nagar, Bilaspur</t>
+          <t>Raj Kishore Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8993,7 +9105,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>2500</t>
@@ -9038,7 +9154,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sarkanda, Bilaspur</t>
+          <t>Sarkanda, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9089,7 +9205,7 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Gauri Ganesh Colony, Bilaspur</t>
+          <t>Gauri Ganesh Colony, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9107,7 +9223,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>3200</t>
@@ -9136,7 +9256,7 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Mangla, Bilaspur</t>
+          <t>Mangla, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9154,7 +9274,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>2500</t>
@@ -9199,7 +9323,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hamu Nagar, Bilaspur</t>
+          <t>Hamu Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9217,7 +9341,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>6500</t>
@@ -9246,7 +9374,7 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ganga Nagar, Bilaspur</t>
+          <t>Ganga Nagar, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9264,7 +9392,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>6000</t>
@@ -9297,7 +9429,7 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sarkanda, Bilaspur</t>
+          <t>Sarkanda, Bilaspur, Chhattisgarh</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9315,7 +9447,11 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>3200</t>
@@ -9324,6 +9460,8304 @@
       <c r="M149" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>room_149_img1.webp</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>room_149_img2.webp</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>room_149_img3.webp</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>room_149_img4.webp</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>room_149_img5.webp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Telibandha, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>room_150_img1.webp</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>room_150_img2.webp</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>room_150_img3.webp</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>room_150_img4.webp</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>room_150_img5.webp</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Mowa, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>room_151_img1.webp</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>room_151_img2.webp</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Nahar Para, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>room_152_img1.webp</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>room_152_img2.webp</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>room_152_img3.webp</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>room_152_img4.webp</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>room_152_img5.webp</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Rajiv Nagar Colony, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>room_153_img1.webp</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>room_153_img2.webp</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>room_153_img3.webp</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>room_153_img4.webp</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>room_153_img5.webp</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Kabeer Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>room_154_img1.webp</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>room_154_img2.webp</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>room_154_img3.webp</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Pachpedi Naka, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>room_155_img1.webp</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>room_155_img2.webp</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>room_155_img3.webp</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>room_155_img4.webp</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Kota, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>room_156_img1.webp</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>room_156_img2.webp</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>room_156_img3.webp</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>room_156_img4.webp</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>room_156_img5.webp</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Shyam Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>room_157_img1.webp</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>room_157_img2.webp</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>room_157_img3.webp</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Danganiya, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>room_158_img1.webp</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>room_158_img2.webp</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>room_158_img3.webp</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>room_158_img4.webp</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>room_158_img5.webp</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Kotwali Chowk, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>room_159_img1.webp</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>room_159_img2.webp</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>room_159_img3.webp</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>room_159_img4.webp</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>room_159_img5.webp</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Matpara, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>room_160_img1.webp</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>room_160_img2.webp</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>room_160_img3.webp</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>room_160_img4.webp</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>room_160_img5.webp</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>room_161_img1.webp</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Avanti Vihar Colony, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>room_162_img1.webp</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>room_162_img2.webp</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>room_162_img3.webp</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>room_162_img4.webp</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>room_162_img5.webp</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Mowa, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>room_163_img1.webp</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>room_163_img2.webp</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>room_163_img3.webp</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>room_163_img4.webp</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Kota, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>room_164_img1.webp</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Kanchanjanga Colony, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>room_165_img1.webp</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>room_165_img3.webp</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Mowa, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>room_166_img1.webp</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>room_166_img2.webp</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>room_166_img3.webp</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>room_166_img4.webp</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>room_166_img5.webp</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Pachpedi Naka, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>room_167_img1.webp</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>room_167_img2.webp</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>room_167_img3.webp</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>room_167_img4.webp</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>room_167_img5.webp</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Mangal Bazar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>room_168_img1.webp</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>room_168_img2.webp</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>room_168_img3.webp</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>room_168_img4.webp</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>room_168_img5.webp</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Kota, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>room_169_img1.webp</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>room_169_img2.webp</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>room_169_img3.webp</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Mangal Bazar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>room_170_img1.webp</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>room_170_img2.webp</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>room_170_img3.webp</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>room_170_img4.webp</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Mahavir Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>room_171_img1.webp</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>room_171_img2.webp</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>room_171_img3.webp</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>room_171_img4.webp</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>room_171_img5.webp</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Ravi Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>room_172_img1.webp</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>room_172_img2.webp</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>room_172_img3.webp</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>room_172_img4.webp</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>room_172_img5.webp</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Fafadih, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>room_173_img1.webp</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>room_173_img2.webp</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>room_173_img3.webp</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Sunder Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>room_174_img1.webp</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>room_174_img2.webp</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>room_174_img3.webp</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>room_174_img4.webp</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Professor Colony, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>room_175_img1.webp</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>room_175_img2.webp</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>room_175_img3.webp</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>room_175_img4.webp</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>room_175_img5.webp</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>New Shanti Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>room_176_img1.webp</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>room_176_img2.webp</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>room_176_img3.webp</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>room_176_img4.webp</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>room_176_img5.webp</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Gopiapara, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>room_177_img1.webp</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>room_177_img2.webp</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>room_177_img3.webp</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>room_177_img4.webp</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>room_177_img5.webp</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>New Rajendra Nagar, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>room_178_img1.webp</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>room_178_img2.webp</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Avanti Vihar Colony, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>room_179_img1.webp</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Kota Colony, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>room_180_img1.webp</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>room_180_img2.webp</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>room_180_img3.webp</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>room_180_img4.webp</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>room_180_img5.webp</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Mominpara, Raipur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>room_181_img1.webp</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>room_181_img2.webp</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>room_181_img3.webp</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>room_181_img4.webp</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>room_181_img5.webp</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Supele Market, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>room_182_img1.webp</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>room_182_img2.webp</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>room_182_img3.webp</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>room_182_img4.webp</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>room_182_img5.webp</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Kripal Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>room_183_img1.webp</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>room_183_img2.webp</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>room_183_img3.webp</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Jamul, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>room_184_img1.webp</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>room_184_img2.webp</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>room_184_img3.webp</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>room_184_img4.webp</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>room_184_img5.webp</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>room_185_img1.webp</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>room_185_img2.webp</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>room_185_img3.webp</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Ram nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>room_186_img1.webp</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>room_186_img2.webp</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>room_186_img3.webp</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>room_186_img4.webp</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>room_186_img5.webp</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Vaishali Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>room_187_img1.webp</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>room_187_img2.webp</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>room_187_img3.webp</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>room_187_img4.webp</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>room_187_img5.webp</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Kripal Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>room_188_img1.webp</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>room_188_img2.webp</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Housing Board Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>room_189_img1.webp</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>room_189_img2.webp</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>room_189_img3.webp</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Ram nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>room_190_img1.webp</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>room_190_img3.webp</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>room_190_img4.webp</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>room_190_img5.webp</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Vaishali Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>room_191_img1.webp</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>room_191_img2.webp</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>room_191_img3.webp</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>room_191_img4.webp</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>room_191_img5.webp</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Kripal Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>7800</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>room_192_img1.webp</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>room_192_img2.webp</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>room_192_img3.webp</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Supele Market, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>room_193_img1.webp</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>room_193_img2.webp</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>room_193_img3.webp</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>room_193_img4.webp</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>room_193_img5.webp</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Kohka Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>room_194_img1.webp</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Radhika Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>room_195_img1.webp</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>room_195_img2.webp</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Hind Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>room_196_img1.webp</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>room_196_img2.webp</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>room_196_img3.webp</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>room_196_img4.webp</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>room_196_img5.webp</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Arya Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>room_197_img1.webp</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>room_197_img2.webp</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>room_197_img3.webp</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>room_197_img4.webp</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>room_197_img5.webp</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Arya Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>room_198_img1.webp</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>room_198_img2.webp</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>room_198_img3.webp</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>room_198_img4.webp</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>room_198_img5.webp</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>room_199_img1.webp</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>room_199_img2.webp</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>room_199_img3.webp</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>room_199_img4.webp</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>room_199_img5.webp</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Kurud, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>room_200_img1.webp</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>room_200_img2.webp</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Maitri nagar Near Dixit Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>room_201_img1.webp</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>room_201_img2.webp</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>room_201_img3.webp</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>room_201_img4.webp</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Shanti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>room_202_img1.webp</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>room_202_img2.webp</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Panchsheel Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>room_203_img1.webp</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>room_203_img2.webp</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>room_203_img3.webp</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>room_203_img4.webp</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>room_203_img5.webp</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Awadhpuri Risali, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>room_204_img1.webp</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>room_204_img2.webp</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>room_204_img3.webp</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>room_204_img4.webp</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>room_204_img5.webp</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Pushpak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>room_205_img1.webp</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>room_205_img2.webp</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>room_205_img3.webp</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>room_205_img4.webp</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>room_205_img5.webp</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Madhuban Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>room_206_img1.webp</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>room_206_img2.webp</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>room_206_img4.webp</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>room_206_img5.webp</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Maitri Kunj, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>room_207_img1.webp</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>room_208_img1.webp</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>room_208_img2.webp</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>room_208_img3.webp</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>room_208_img4.webp</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>room_208_img5.webp</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Kadambari Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>room_209_img1.webp</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>room_209_img2.webp</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>room_209_img3.webp</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>room_210_img1.webp</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>room_210_img2.webp</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Hari Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>room_211_img1.webp</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>room_211_img2.webp</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>room_211_img3.webp</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>room_211_img4.webp</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>room_211_img5.webp</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Ruabandha, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>room_212_img1.webp</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>room_212_img2.webp</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>room_212_img3.webp</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>room_212_img4.webp</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>room_212_img5.webp</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>room_213_img1.webp</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>room_213_img2.webp</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>room_213_img3.webp</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>room_213_img4.webp</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>room_213_img5.webp</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Vishwa Bank Housing Board Colony, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>room_214_img1.webp</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>room_214_img2.webp</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Surya Vihar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>room_215_img1.webp</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>room_215_img2.webp</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>room_215_img3.webp</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>room_215_img4.webp</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>room_215_img5.webp</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Kurud, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>room_216_img1.webp</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>room_216_img2.webp</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>room_216_img3.webp</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>room_216_img4.webp</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>room_216_img5.webp</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Subash Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>room_217_img1.webp</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>room_217_img2.webp</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>room_217_img3.webp</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>room_217_img4.webp</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>room_217_img5.webp</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Hasharidih Durg, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>room_218_img1.webp</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>room_218_img2.webp</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>room_218_img3.webp</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Kasaridih, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>room_219_img1.webp</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Jay Bhim Nagar, Durg, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>room_220_img1.webp</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Junwani, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>room_221_img1.webp</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>room_221_img2.webp</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Nehru Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>room_222_img1.webp</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Chauhan Town, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>room_223_img1.webp</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>room_223_img2.webp</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>room_223_img3.webp</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>room_223_img4.webp</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>room_223_img5.webp</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>room_224_img1.webp</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>room_224_img2.webp</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Chauhan Town, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>room_225_img1.webp</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Chauhan Town, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>room_226_img1.webp</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>room_226_img2.webp</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>room_226_img3.webp</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>room_226_img4.webp</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>room_226_img5.webp</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Hudco, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>14000</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>room_227_img1.webp</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>room_227_img2.webp</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>room_227_img3.webp</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>room_227_img4.webp</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>room_227_img5.webp</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Smriti Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>room_228_img1.webp</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>room_228_img2.webp</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Anand Nagar Near Puspak Nagar, Bhilai, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Semi-furnished</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>room_229_img1.webp</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>room_229_img2.webp</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>room_229_img3.webp</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>room_229_img4.webp</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>room_229_img5.webp</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Sharda Vihar, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>room_230_img1.webp</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>room_230_img2.webp</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>room_230_img3.webp</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>room_230_img4.webp</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>room_230_img5.webp</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Ravi Shankar Shukla Nagar, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>room_231_img1.webp</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>room_231_img2.webp</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Purani Basti, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>room_232_img1.webp</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>room_232_img2.webp</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>room_232_img3.webp</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>room_232_img4.webp</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>room_232_img5.webp</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Hig Colony, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>room_233_img1.webp</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>room_233_img2.webp</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>room_233_img3.webp</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>room_233_img4.webp</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>room_233_img5.webp</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Sharda Vihar, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>room_234_img1.webp</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>room_234_img2.webp</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>room_234_img3.webp</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Patel Para, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>room_235_img1.webp</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>room_235_img2.webp</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>room_235_img3.webp</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>room_235_img4.webp</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>room_235_img5.webp</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Marapara, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>room_236_img1.webp</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Shahid Bhagat Singh Colony, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>room_237_img1.webp</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>room_237_img2.webp</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>room_237_img3.webp</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>room_237_img4.webp</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>room_237_img5.webp</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Jungle Colony, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>room_238_img1.webp</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>room_238_img2.webp</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>room_238_img3.webp</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>room_238_img4.webp</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>room_238_img5.webp</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Sharda Vihar, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>room_239_img1.webp</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>room_239_img2.webp</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>room_239_img3.webp</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Balco Nagar, Korba, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>room_240_img1.webp</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>room_240_img2.webp</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>room_240_img3.webp</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>room_240_img4.webp</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>room_240_img5.webp</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Kachahri Chowk, Janjgir, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>room_241_img1.webp</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>room_241_img2.webp</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>room_241_img3.webp</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>room_241_img4.webp</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>room_241_img5.webp</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Dharampura, Jagdalpur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>room_242_img1.webp</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>room_242_img2.webp</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>room_242_img3.webp</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>room_242_img4.webp</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>room_242_img5.webp</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Dharampura, Jagdalpur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>room_243_img1.webp</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>room_243_img2.webp</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Kumhar Para, Jagdalpur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>room_244_img1.webp</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>room_244_img2.webp</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>room_244_img3.webp</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>room_244_img4.webp</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>room_244_img5.webp</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Sun City, Jagdalpur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>room_245_img1.webp</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Bangala Para, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>room_246_img1.webp</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>room_246_img2.webp</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>room_246_img3.webp</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Chakaradhar Nagar, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>furnished</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>room_247_img1.webp</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>room_247_img2.webp</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>room_247_img3.webp</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>room_247_img4.webp</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>room_247_img5.webp</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Bank Colony, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>room_248_img1.webp</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>room_248_img2.webp</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>room_248_img3.webp</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>room_248_img4.webp</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Dindayal Puram, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>room_249_img1.webp</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>room_249_img2.webp</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>room_249_img3.webp</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>room_249_img4.webp</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>room_249_img5.webp</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>EWS Colony, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>room_250_img1.webp</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>room_250_img2.webp</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>room_250_img3.webp</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>room_250_img4.webp</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>room_250_img5.webp</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Krishn Vihar, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>room_251_img1.webp</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Dhangar Deepa, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>room_252_img1.webp</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>room_252_img2.webp</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>room_252_img3.webp</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>room_252_img4.webp</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>room_252_img5.webp</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Jagannath Puram, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>room_253_img1.webp</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Dindayal Puram, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>room_254_img1.webp</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>room_254_img2.webp</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>room_254_img3.webp</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>room_254_img4.webp</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>room_254_img5.webp</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Chakaradhar Nagar, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>room_255_img1.webp</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>room_255_img2.webp</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>room_255_img3.webp</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>room_255_img4.webp</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Kirodimal Nagar, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>room_256_img1.webp</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>room_256_img2.webp</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>room_256_img3.webp</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Kirodimal Nagar, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>room_257_img1.webp</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>room_257_img2.webp</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Kirodimal Nagar, Raigarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>room_258_img1.webp</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>room_258_img2.webp</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>room_258_img3.webp</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>room_258_img4.webp</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>room_258_img5.webp</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Jhandapada, Belpahar, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>room_259_img1.webp</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>room_259_img2.webp</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>room_259_img3.webp</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>room_259_img4.webp</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>room_259_img5.webp</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Ratan Mahka, Kharsia, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>room_260_img1.webp</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>room_260_img2.webp</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>room_260_img3.webp</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>room_260_img4.webp</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Bhatra, Sambalpur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>room_261_img1.webp</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>room_261_img2.webp</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>room_261_img3.webp</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Marwari Para, Jharsuguda, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Power Backup, Wifi</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>room_262_img1.webp</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>room_262_img2.webp</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>room_262_img3.webp</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>room_262_img4.webp</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>room_262_img5.webp</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Marwari Para, Jharsuguda, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>room_263_img1.webp</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>room_263_img2.webp</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>room_263_img3.webp</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Islam Mohalla, Saraipali, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Water Supply</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>room_264_img1.webp</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>room_264_img2.webp</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>room_264_img3.webp</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>room_264_img4.webp</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>room_264_img5.webp</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Malidih, Sundargarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>room_265_img1.webp</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>room_265_img2.webp</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>room_265_img3.webp</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Ranibagicha, Sundargarh, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>room_266_img1.webp</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Dora Colony, Sambalpur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>room_267_img1.webp</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>room_267_img2.webp</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Canal Colony, Khaliapali, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>room_268_img1.webp</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>room_268_img2.webp</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>room_268_img3.webp</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>room_268_img4.webp</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>room_268_img5.webp</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Puranabasti, Jharsuguda, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>room_269_img1.webp</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>room_269_img2.webp</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>room_269_img3.webp</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>room_269_img4.webp</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>room_269_img5.webp</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Basant Vihar, Jharsuguda, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>5800</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>room_270_img1.webp</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>room_270_img2.webp</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>room_270_img3.webp</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>room_270_img4.webp</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Marwari Para, Jharsuguda, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>room_271_img1.webp</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>room_271_img2.webp</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>room_271_img3.webp</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>room_271_img4.webp</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Gujarati Colony, Sambalpur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>room_272_img1.webp</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>room_272_img2.webp</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>room_272_img3.webp</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>room_272_img4.webp</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>room_272_img5.webp</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Ekatali, Jharsuguda, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>room_273_img1.webp</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>room_273_img2.webp</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>room_273_img3.webp</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>room_273_img4.webp</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>room_273_img5.webp</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Maya Pur, Ambikapur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>room_274_img1.webp</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>room_274_img2.webp</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>room_274_img3.webp</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>room_274_img4.webp</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>room_274_img5.webp</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Laxmipur, Phunderdihari, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>room_275_img1.webp</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Maya Pur, Ambikapur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>room_276_img1.webp</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Sadwar, Ambikapur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>room_277_img2.webp</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>room_277_img3.webp</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>room_277_img4.webp</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>room_277_img5.webp</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Bandhwapara, Bilaspur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>CCTV</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>room_278_img2.webp</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>room_278_img3.webp</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>room_278_img4.webp</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>room_278_img5.webp</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Gauri Ganesh Colony, Bilaspur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>room_279_img3.webp</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>room_279_img4.webp</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>room_279_img5.webp</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>room_280_img1.webp</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>room_280_img2.webp</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Sarkanda, Bilaspur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>room_281_img1.webp</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>room_281_img2.webp</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>27 Kholi, Bilaspur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>room_282_img1.webp</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>room_282_img2.webp</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>room_282_img3.webp</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Agyeya Nagar, Bilaspur, Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
